--- a/DOSSIES_MULTIFORMATO/CETAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CETAM/dossie.xlsx
@@ -688,17 +688,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023NE0001573</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>2023NE0001574</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7/2020</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>29/11/2023</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>100000</v>
+        <v>923541.27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -707,14 +711,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Referente a anulação da NE 1507/2023.</t>
+          <t>contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do cetam. Parecer juridico - 2023 -PJ/CETAM pag. 28 a 33. TC: 007/202</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023NE0001563</t>
+          <t>2023NE0001570</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -728,7 +732,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>334735.1</v>
+        <v>780039.12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -744,7 +748,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023NE0001570</t>
+          <t>2023NE0001563</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -758,7 +762,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>780039.12</v>
+        <v>334735.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -774,21 +778,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023NE0001574</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7/2020</t>
-        </is>
-      </c>
+          <t>2023NE0001573</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>29/11/2023</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>923541.27</v>
+        <v>100000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do cetam. Parecer juridico - 2023 -PJ/CETAM pag. 28 a 33. TC: 007/202</t>
+          <t>Referente a anulação da NE 1507/2023.</t>
         </is>
       </c>
     </row>
@@ -894,10 +894,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2018NE01868</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>2018NE01869</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>28/08/2018</t>
@@ -913,21 +917,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>anulação total</t>
+          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2018NE01869</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2018NE01868</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>28/08/2018</t>
@@ -943,19 +943,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
+          <t>anulação total</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025NE0000084</t>
+          <t>2025NE0000083</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>699789.98</v>
+        <v>371098.88</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -973,19 +973,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025NE0000083</t>
+          <t>2025NE0000084</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>371098.88</v>
+        <v>699789.98</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024NE0001976</t>
+          <t>2024NE0001977</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>185549.44</v>
+        <v>10779.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024NE0001975</t>
+          <t>2024NE0001974</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>431973.43</v>
+        <v>349894.99</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1149,19 +1149,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 07.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024NE0001974</t>
+          <t>2024NE0001975</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>349894.99</v>
+        <v>431973.43</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1179,19 +1179,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 07.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024NE0001977</t>
+          <t>2024NE0001976</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10779.72</v>
+        <v>185549.44</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2022NE0003259</t>
+          <t>2022NE0003260</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6636.78</v>
+        <v>302096.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1355,19 +1355,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de Tecnologia da Informação e Comunicação de Dados - TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web.</t>
+          <t>Contratação dos serviços de fornecimento de circuito de transmissão de dados e conexão á rede metropolitana de Manaus Repam/Metromao.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2022NE0003260</t>
+          <t>2022NE0003259</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>302096.8</v>
+        <v>6636.78</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1385,19 +1385,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de fornecimento de circuito de transmissão de dados e conexão á rede metropolitana de Manaus Repam/Metromao.</t>
+          <t>Contratação dos serviços de Tecnologia da Informação e Comunicação de Dados - TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020NE01142</t>
+          <t>2020NE01135</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>414.51</v>
+        <v>546345.0699999999</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1415,19 +1415,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
+          <t>Referente a contratação dos serviços de TI para acesso e manutenção, através da rede Metropolitana de Manaus REPAM/por meio de fibra ótica no CETAM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020NE01136</t>
+          <t>2020NE01146</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>317774.55</v>
+        <v>25160.85</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1445,19 +1445,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Referente fornecimento de consultoria, Manutenção e Suporte de Software em Banco de Dados, desenvolvimento de Sistemas de Informação</t>
+          <t>Contratação dos serviços de desenvolvimento de sistemas de informação, compreendendo a analise e desenvolvimento de funcionalidades em sistema de inscrições e matriculas, para atender demanda do cetam</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020NE01146</t>
+          <t>2020NE01136</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>25160.85</v>
+        <v>317774.55</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1475,19 +1475,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistemas de informação, compreendendo a analise e desenvolvimento de funcionalidades em sistema de inscrições e matriculas, para atender demanda do cetam</t>
+          <t>Referente fornecimento de consultoria, Manutenção e Suporte de Software em Banco de Dados, desenvolvimento de Sistemas de Informação</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020NE01135</t>
+          <t>2020NE01142</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>546345.0699999999</v>
+        <v>414.51</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Referente a contratação dos serviços de TI para acesso e manutenção, através da rede Metropolitana de Manaus REPAM/por meio de fibra ótica no CETAM</t>
+          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2019NE03028</t>
+          <t>2019NE03029</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>984.84</v>
+        <v>736.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1617,14 +1617,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Referente anulação total do saldo da NE nº 1150/19, por ocasião do encerramento do exercício</t>
+          <t>Referente anulação total do saldo da NE nº 1520/19, por ocasião do encerramento do exercício</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2019NE03027</t>
+          <t>2019NE03026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8078.45</v>
+        <v>39373</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1643,14 +1643,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Referente anulação total do saldo da NE nº 1144/19, por ocasião do encerramento do exercício</t>
+          <t>Referente anulação total do saldo da NE nº 1143/19, por ocasião do encerramento do exercício</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2019NE03026</t>
+          <t>2019NE03027</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>39373</v>
+        <v>8078.45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Referente anulação total do saldo da NE nº 1143/19, por ocasião do encerramento do exercício</t>
+          <t>Referente anulação total do saldo da NE nº 1144/19, por ocasião do encerramento do exercício</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2019NE03029</t>
+          <t>2019NE03028</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>736.6</v>
+        <v>984.84</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Referente anulação total do saldo da NE nº 1520/19, por ocasião do encerramento do exercício</t>
+          <t>Referente anulação total do saldo da NE nº 1150/19, por ocasião do encerramento do exercício</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2016NE02320</t>
+          <t>2016NE02319</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>35570</v>
+        <v>1615.69</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1721,14 +1721,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anulação total da NE</t>
+          <t>Anulação do total do saldo da NE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2016NE02319</t>
+          <t>2016NE02320</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1615.69</v>
+        <v>35570</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anulação do total do saldo da NE</t>
+          <t>Anulação total da NE</t>
         </is>
       </c>
     </row>
@@ -1784,21 +1784,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025NE0001416</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>6/2020</t>
-        </is>
-      </c>
+          <t>2025NE0001373</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>23/10/2025</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>719524.0600000001</v>
+        <v>69156.25999999999</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1807,7 +1803,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). T</t>
+          <t>Anulação parcial da Nota de Empenho nº 793/2025.</t>
         </is>
       </c>
     </row>
@@ -1840,17 +1836,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025NE0001373</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>2025NE0001416</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6/2020</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>23/10/2025</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>69156.25999999999</v>
+        <v>719524.0600000001</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anulação parcial da Nota de Empenho nº 793/2025.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). T</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024NE0000446</t>
+          <t>2024NE0000445</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>669470.2</v>
+        <v>10339.26</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1889,19 +1889,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024NE0000445</t>
+          <t>2024NE0000446</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10339.26</v>
+        <v>669470.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1919,14 +1919,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025NE0001370</t>
+          <t>2025NE0001371</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5389.86</v>
+        <v>11098.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1956,12 +1956,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025NE0001365</t>
+          <t>2025NE0001366</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>349894.99</v>
+        <v>469030.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1979,19 +1979,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 09.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025NE0001367</t>
+          <t>2025NE0001369</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>964514.52</v>
+        <v>393877.68</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 10.</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam. TC: 0010/2024 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025NE0001369</t>
+          <t>2025NE0001367</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>393877.68</v>
+        <v>964514.52</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,19 +2069,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam. TC: 0010/2024 AD: 01.</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 10.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025NE0001366</t>
+          <t>2025NE0001365</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>469030.6</v>
+        <v>349894.99</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2099,14 +2099,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 09.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025NE0001371</t>
+          <t>2025NE0001370</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11098.8</v>
+        <v>5389.86</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2166,12 +2166,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2021NE0001029</t>
+          <t>2021NE0001040</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>773141.37</v>
+        <v>953323.65</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2189,19 +2189,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de interligação da rede de computadores das unidades do CETAM mediante fornecimento de circuito de transmissão de dados a rede metropolitana de Manaus (metromao) com proviment</t>
+          <t>Contratação dos serviços de administração e suporte tecnico em banco de dados e sistemas, desenvlimento de sistemas de informação e modelagem de processos de negocio, sob demanda.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2021NE0001040</t>
+          <t>2021NE0001029</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>953323.65</v>
+        <v>773141.37</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de administração e suporte tecnico em banco de dados e sistemas, desenvlimento de sistemas de informação e modelagem de processos de negocio, sob demanda.</t>
+          <t>Contratação dos serviços de interligação da rede de computadores das unidades do CETAM mediante fornecimento de circuito de transmissão de dados a rede metropolitana de Manaus (metromao) com proviment</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2023NE0000982</t>
+          <t>2023NE0000966</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1003719.24</v>
+        <v>890608.04</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2309,19 +2309,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do cetam. Parecer juridico - 2023 -PJ/CETAM pag. 28 a 33. TC: 007/202</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2023NE0000966</t>
+          <t>2023NE0000982</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>890608.04</v>
+        <v>1003719.24</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do cetam. Parecer juridico - 2023 -PJ/CETAM pag. 28 a 33. TC: 007/202</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024NE0000209</t>
+          <t>2024NE0000207</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2568.98</v>
+        <v>117619.83</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Referente a contratação dos serviços de e Tecnologia da Informação e Comunicação de Dados – TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web, no</t>
+          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024NE0000210</t>
+          <t>2024NE0000205</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6010.2</v>
+        <v>493733.79</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2459,19 +2459,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Referente a contratação dos serviços de e Tecnologia da Informação e Comunicação de Dados – TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web, no</t>
+          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024NE0000200</t>
+          <t>2024NE0000206</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11812</v>
+        <v>480566.06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2489,19 +2489,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente a contratação de serviços de Sistemas de Infraestrutura, compreendendo os serviços de Instalação, Hospedagem de Servidores e Suporte em Sistemas de Informação nas unidades do Cetam.Contrato </t>
+          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024NE0000208</t>
+          <t>2024NE0000204</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3837.14</v>
+        <v>522954.96</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2519,19 +2519,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Referente a contratação dos serviços de e Tecnologia da Informação e Comunicação de Dados – TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web, no</t>
+          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024NE0000204</t>
+          <t>2024NE0000208</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>522954.96</v>
+        <v>3837.14</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2549,19 +2549,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
+          <t>Referente a contratação dos serviços de e Tecnologia da Informação e Comunicação de Dados – TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web, no</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024NE0000206</t>
+          <t>2024NE0000200</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>480566.06</v>
+        <v>11812</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2579,19 +2579,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
+          <t xml:space="preserve">Referente a contratação de serviços de Sistemas de Infraestrutura, compreendendo os serviços de Instalação, Hospedagem de Servidores e Suporte em Sistemas de Informação nas unidades do Cetam.Contrato </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024NE0000205</t>
+          <t>2024NE0000210</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>493733.79</v>
+        <v>6010.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2609,19 +2609,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
+          <t>Referente a contratação dos serviços de e Tecnologia da Informação e Comunicação de Dados – TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web, no</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024NE0000207</t>
+          <t>2024NE0000209</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>117619.83</v>
+        <v>2568.98</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente a contratação dos Serviços de de Administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negocio, sob demanda. No </t>
+          <t>Referente a contratação dos serviços de e Tecnologia da Informação e Comunicação de Dados – TIC, compreendendo a execução dos sistemas SPROWEB e PRODAMRH e licença de uso do Gestor de Conteúdo Web, no</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2021NE0001017</t>
+          <t>2021NE0001016</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1469.54</v>
+        <v>682.6799999999999</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2725,14 +2725,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anulação do saldo de empenho</t>
+          <t>Anulação do saldo do empenho</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2021NE0001016</t>
+          <t>2021NE0001017</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>682.6799999999999</v>
+        <v>1469.54</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anulação do saldo do empenho</t>
+          <t>Anulação do saldo de empenho</t>
         </is>
       </c>
     </row>
@@ -2788,21 +2788,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2022NE0003505</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>6/2020</t>
-        </is>
-      </c>
+          <t>2022NE0003502</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>19/12/2022</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15916.44</v>
+        <v>29.82</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2811,7 +2807,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de fornecimento de circuito de transmissão de dados e conexão á rede metropolitana de Manaus Repam/Metromao, atendendo as necessidades deste órgão de Educação Profissional.</t>
+          <t>Cancelamento da NE 745/2022 pelo encerramento do exercício</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2840,21 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2022NE0003502</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>2022NE0003505</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>6/2020</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>19/12/2022</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>29.82</v>
+        <v>15916.44</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cancelamento da NE 745/2022 pelo encerramento do exercício</t>
+          <t>Contratação dos serviços de fornecimento de circuito de transmissão de dados e conexão á rede metropolitana de Manaus Repam/Metromao, atendendo as necessidades deste órgão de Educação Profissional.</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2021NE0000182</t>
+          <t>2021NE0000185</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>127154.19</v>
+        <v>48948.16</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2979,19 +2979,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de circuito de transmissão de dados e acesso gerenciado a Rede Mundial _ internet.</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2021NE0000184</t>
+          <t>2021NE0000186</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>24870.8</v>
+        <v>1030855.16</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
+          <t>Contratação dos serviços de interligação da rede de computadores das unidades do CETAM mediante fornecimento de circuito de transmissão de dados a rede metropolitana de Manaus (metromao) com proviment</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2021NE0000186</t>
+          <t>2021NE0000184</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1030855.16</v>
+        <v>24870.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3039,19 +3039,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de interligação da rede de computadores das unidades do CETAM mediante fornecimento de circuito de transmissão de dados a rede metropolitana de Manaus (metromao) com proviment</t>
+          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2021NE0000185</t>
+          <t>2021NE0000182</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>48948.16</v>
+        <v>127154.19</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3069,14 +3069,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação dos serviços de circuito de transmissão de dados e acesso gerenciado a Rede Mundial _ internet.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2017NE02029</t>
+          <t>2017NE02026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10625.96</v>
+        <v>522.88</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3095,14 +3095,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE, devido encerramento do exercício de 2017.</t>
+          <t>Anulação do saldo da NE</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2017NE02028</t>
+          <t>2017NE01988</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7662.48</v>
+        <v>813.3</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3121,14 +3121,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE</t>
+          <t>Anulação do saldo de empenho</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2017NE02027</t>
+          <t>2017NE02031</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5129.37</v>
+        <v>7597.67</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE</t>
+          <t>Anulação do saldo da NE, devido encerramento do exercício de 2017.</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2017NE02031</t>
+          <t>2017NE02027</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7597.67</v>
+        <v>5129.37</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3199,14 +3199,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE, devido encerramento do exercício de 2017.</t>
+          <t>Anulação do saldo da NE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2017NE01988</t>
+          <t>2017NE02028</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>813.3</v>
+        <v>7662.48</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3225,14 +3225,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Anulação do saldo de empenho</t>
+          <t>Anulação do saldo da NE</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2017NE02026</t>
+          <t>2017NE02029</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>522.88</v>
+        <v>10625.96</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3251,14 +3251,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE</t>
+          <t>Anulação do saldo da NE, devido encerramento do exercício de 2017.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2015NE03060</t>
+          <t>2015NE03089</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>877.1799999999999</v>
+        <v>7914.48</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE nº 36</t>
+          <t>Anulação total do saldo da NE</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2015NE03089</t>
+          <t>2015NE03060</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7914.48</v>
+        <v>877.1799999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE</t>
+          <t>Anulação do saldo da NE nº 36</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2016NE02194</t>
+          <t>2016NE02195</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2462.46</v>
+        <v>2216.58</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2016NE02195</t>
+          <t>2016NE02194</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2216.58</v>
+        <v>2462.46</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2017NE01902</t>
+          <t>2017NE01906</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>8794.52</v>
+        <v>35565.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2017NE01906</t>
+          <t>2017NE01902</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>35565.1</v>
+        <v>8794.52</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3871,19 +3871,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2022NE0000808</t>
+          <t>2022NE0000809</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1934134.76</v>
+        <v>1711699.84</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3901,19 +3901,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE ADMINISTRAÇÃO E SUPORTE TÉCNICO EM BANCO DE DADOS E SISTEMAS, DESENVOLVIMENTO DE SISTEMAS DE INFORMAÇÃO E MODELAGEM DE PROCESSOS DE NEGOCIO, SOB DEMANDA.</t>
+          <t>Contratação dos serviços de interligação das redes de computadores das unidades do cetam mediante fornecimento de circuito de transmissao de dados e conexao a rede metropolitana de Manaus (metromao).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2022NE0000809</t>
+          <t>2022NE0000808</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711699.84</v>
+        <v>1934134.76</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de interligação das redes de computadores das unidades do cetam mediante fornecimento de circuito de transmissao de dados e conexao a rede metropolitana de Manaus (metromao).</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE ADMINISTRAÇÃO E SUPORTE TÉCNICO EM BANCO DE DADOS E SISTEMAS, DESENVOLVIMENTO DE SISTEMAS DE INFORMAÇÃO E MODELAGEM DE PROCESSOS DE NEGOCIO, SOB DEMANDA.</t>
         </is>
       </c>
     </row>
@@ -3968,12 +3968,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2019NE02185</t>
+          <t>2019NE02186</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>28366.2</v>
+        <v>75482.55</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3991,19 +3991,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação de empresa especializada para implantação de sistemas de informação, compreendendo análise e desenvolvimento de funcionalidades em sistema: Inscrição de Processo Seletivo e Matrícula.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2019NE02186</t>
+          <t>2019NE02185</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>75482.55</v>
+        <v>28366.2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para implantação de sistemas de informação, compreendendo análise e desenvolvimento de funcionalidades em sistema: Inscrição de Processo Seletivo e Matrícula.</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
@@ -4118,12 +4118,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2019NE01143</t>
+          <t>2019NE01144</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>118119</v>
+        <v>17098.47</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Contratação dos serviços para acesso a internet</t>
+          <t>Contratação dos serviços de execução dos sistemas sproweb, prodam e licença do uso de gestor conteúdo web.</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4178,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2019NE01144</t>
+          <t>2019NE01143</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>17098.47</v>
+        <v>118119</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução dos sistemas sproweb, prodam e licença do uso de gestor conteúdo web.</t>
+          <t>Contratação dos serviços para acesso a internet</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2016NE01738</t>
+          <t>2016NE01742</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>26169.38</v>
+        <v>600.36</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Anulação total</t>
+          <t>Ref. anulação do saldo da NE nº 1211</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2016NE01743</t>
+          <t>2016NE01749</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3373.79</v>
+        <v>5158.03</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4313,14 +4313,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 16</t>
+          <t>Ref. anulação da NE nº 1711</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2016NE01745</t>
+          <t>2016NE01749</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>3070.87</v>
+        <v>5158.03</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4339,24 +4339,28 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 713</t>
+          <t>Ref. anulação da NE nº 1711</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2016NE01739</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2016NE01751</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>26.76</v>
+        <v>5158.03</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4365,24 +4369,28 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 37</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2016NE01743</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>2016NE01686</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3373.79</v>
+        <v>35570</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4391,24 +4399,28 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 16</t>
+          <t>Ref. serviço de transmissão de dados</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2016NE01746</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>2016NE01686</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3011.02</v>
+        <v>35570</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4417,24 +4429,28 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 1213</t>
+          <t>Ref. serviço de transmissão de dados</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2016NE01741</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>2016NE01751</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5772.41</v>
+        <v>5158.03</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4443,14 +4459,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 40</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2016NE01738</t>
+          <t>2016NE01741</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4460,7 +4476,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>26169.38</v>
+        <v>5772.41</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4469,14 +4485,14 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anulação total</t>
+          <t>Ref. anulação do saldo da NE nº 40</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2016NE01739</t>
+          <t>2016NE01746</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -4486,7 +4502,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>26.76</v>
+        <v>3011.02</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4495,24 +4511,28 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 37</t>
+          <t>Ref. anulação do saldo da NE nº 1213</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2016NE01745</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2016NE01711</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3070.87</v>
+        <v>5158.03</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4521,28 +4541,24 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 713</t>
+          <t>Serviço de Tecnologia e Informação</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2016NE01711</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01742</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5158.03</v>
+        <v>600.36</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4551,24 +4567,28 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Serviço de Tecnologia e Informação</t>
+          <t>Ref. anulação do saldo da NE nº 1211</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2016NE01742</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>2016NE01711</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>600.36</v>
+        <v>5158.03</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4577,28 +4597,24 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 1211</t>
+          <t>Serviço de Tecnologia e Informação</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2016NE01711</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01745</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5158.03</v>
+        <v>3070.87</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4607,14 +4623,14 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Serviço de Tecnologia e Informação</t>
+          <t>Ref. anulação do saldo da NE nº 713</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2016NE01746</t>
+          <t>2016NE01739</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -4624,7 +4640,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3011.02</v>
+        <v>26.76</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4633,14 +4649,14 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 1213</t>
+          <t>Ref. anulação do saldo da NE nº 37</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2016NE01741</t>
+          <t>2016NE01738</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -4650,7 +4666,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5772.41</v>
+        <v>26169.38</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4659,28 +4675,24 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 40</t>
+          <t>Anulação total</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2016NE01751</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01741</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5158.03</v>
+        <v>5772.41</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4689,28 +4701,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Ref. anulação do saldo da NE nº 40</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2016NE01686</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2016NE01746</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>35570</v>
+        <v>3011.02</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4719,28 +4727,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ref. serviço de transmissão de dados</t>
+          <t>Ref. anulação do saldo da NE nº 1213</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2016NE01686</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2016NE01743</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>35570</v>
+        <v>3373.79</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4749,28 +4753,24 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ref. serviço de transmissão de dados</t>
+          <t>Ref. anulação do saldo da NE nº 16</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2016NE01751</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01739</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>06/10/2016</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5158.03</v>
+        <v>26.76</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4779,14 +4779,14 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Ref. anulação do saldo da NE nº 37</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2016NE01749</t>
+          <t>2016NE01745</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>5158.03</v>
+        <v>3070.87</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4805,14 +4805,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ref. anulação da NE nº 1711</t>
+          <t>Ref. anulação do saldo da NE nº 713</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2016NE01749</t>
+          <t>2016NE01743</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>5158.03</v>
+        <v>3373.79</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4831,14 +4831,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ref. anulação da NE nº 1711</t>
+          <t>Ref. anulação do saldo da NE nº 16</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2016NE01742</t>
+          <t>2016NE01738</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>600.36</v>
+        <v>26169.38</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ref. anulação do saldo da NE nº 1211</t>
+          <t>Anulação total</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2024NE0000668</t>
+          <t>2024NE0000667</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>167410</v>
+        <v>138001.45</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2024NE0000667</t>
+          <t>2024NE0000668</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>138001.45</v>
+        <v>167410</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4984,12 +4984,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025NE0000185</t>
+          <t>2025NE0000184</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>371098.88</v>
+        <v>10779.72</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5007,19 +5007,19 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025NE0000187</t>
+          <t>2025NE0000186</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>863946.86</v>
+        <v>699789.98</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5037,19 +5037,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 08.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025NE0000186</t>
+          <t>2025NE0000187</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>699789.98</v>
+        <v>863946.86</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5067,19 +5067,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 08.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025NE0000184</t>
+          <t>2025NE0000185</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>10779.72</v>
+        <v>371098.88</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5097,19 +5097,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2024NE0000114</t>
+          <t>2024NE0000115</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>669470.2</v>
+        <v>10339.26</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5127,19 +5127,19 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2024NE0000115</t>
+          <t>2024NE0000114</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>10339.26</v>
+        <v>669470.2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5220,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025NE0000437</t>
+          <t>2025NE0000436</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>699789.98</v>
+        <v>371098.88</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025NE0000436</t>
+          <t>2025NE0000437</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>371098.88</v>
+        <v>699789.98</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2019NE00339</t>
+          <t>2019NE00340</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>17098.47</v>
+        <v>118119</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5419,19 +5419,19 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Contratação de serviços de execução dos sistemas sproweb, prodam - rh e licença do uso de gestor de conteúdo web.</t>
+          <t>Contratação dos serviços de acesso a internet.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2019NE00340</t>
+          <t>2019NE00339</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>118119</v>
+        <v>17098.47</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de acesso a internet.</t>
+          <t>Contratação de serviços de execução dos sistemas sproweb, prodam - rh e licença do uso de gestor de conteúdo web.</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5486,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026NE0000008</t>
+          <t>2026NE0000005</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>22197.6</v>
+        <v>1439048.12</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). T</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5546,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026NE0000005</t>
+          <t>2026NE0000008</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1439048.12</v>
+        <v>22197.6</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5569,19 +5569,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). T</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2015NE00042</t>
+          <t>2015NE00035</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5967</v>
+        <v>5398.68</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5606,12 +5606,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2015NE00035</t>
+          <t>2015NE00042</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5398.68</v>
+        <v>5967</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5636,12 +5636,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2024NE0001724</t>
+          <t>2024NE0001723</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>349894.99</v>
+        <v>431973.43</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 07.</t>
         </is>
       </c>
     </row>
@@ -5696,12 +5696,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2024NE0001723</t>
+          <t>2024NE0001724</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5710,7 +5710,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>431973.43</v>
+        <v>349894.99</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 07.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021NE0000017</t>
+          <t>2021NE0000022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>169538.92</v>
+        <v>19660.76</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5869,19 +5869,19 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de circuito de transmissão de dados e acesso gerenciado a Rede Mundial _ internet.</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021NE0000018</t>
+          <t>2021NE0000032</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>24870.8</v>
+        <v>1271098.2</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5899,19 +5899,19 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
+          <t>Contratação dos serviços de administração e suporte tecnico em banco de dados e sistemas, desenovlimento de sistemas de informação e modelagem de processos de negocio, sob demanda.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021NE0000032</t>
+          <t>2021NE0000018</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1271098.2</v>
+        <v>24870.8</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5929,19 +5929,19 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de administração e suporte tecnico em banco de dados e sistemas, desenovlimento de sistemas de informação e modelagem de processos de negocio, sob demanda.</t>
+          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021NE0000022</t>
+          <t>2021NE0000017</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>19660.76</v>
+        <v>169538.92</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5959,19 +5959,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação dos serviços de circuito de transmissão de dados e acesso gerenciado a Rede Mundial _ internet.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2016NE00037</t>
+          <t>2016NE00016</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>13138.14</v>
+        <v>7483.28</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Ref. contratação de serviço de processamento de dados</t>
         </is>
       </c>
     </row>
@@ -6026,12 +6026,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2016NE00016</t>
+          <t>2016NE00037</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>7483.28</v>
+        <v>13138.14</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ref. contratação de serviço de processamento de dados</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
@@ -6138,12 +6138,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2022NE0000023</t>
+          <t>2022NE0000006</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711699.84</v>
+        <v>24447.12</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6161,19 +6161,19 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de interligação das redes de computadores das unidades do cetam mediante fornecimento de circuito de transmissao de dados e conexao a rede metropolitana de Manaus (metromao).</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2022NE0000006</t>
+          <t>2022NE0000023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>24447.12</v>
+        <v>1711699.84</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM.</t>
+          <t>Contratação dos serviços de interligação das redes de computadores das unidades do cetam mediante fornecimento de circuito de transmissao de dados e conexao a rede metropolitana de Manaus (metromao).</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2024NE0001550</t>
+          <t>2024NE0001549</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>334735.1</v>
+        <v>5169.63</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6251,19 +6251,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2024NE0001549</t>
+          <t>2024NE0001550</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>5169.63</v>
+        <v>334735.1</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6281,19 +6281,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2024NE0001220</t>
+          <t>2024NE0001219</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>334735.1</v>
+        <v>5169.63</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6311,19 +6311,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2024NE0001219</t>
+          <t>2024NE0001220</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>5169.63</v>
+        <v>334735.1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025NE0000795</t>
+          <t>2025NE0000794</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>938061.2</v>
+        <v>10779.72</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6431,19 +6431,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 09.</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025NE0000793</t>
+          <t>2025NE0000792</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>699789.98</v>
+        <v>371098.88</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6461,19 +6461,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025NE0000792</t>
+          <t>2025NE0000793</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>371098.88</v>
+        <v>699789.98</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6491,19 +6491,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025NE0000794</t>
+          <t>2025NE0000795</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>10779.72</v>
+        <v>938061.2</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 09.</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6558,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2017NE00628</t>
+          <t>2017NE00598</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>35178.08</v>
+        <v>20632.13</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ref. serviço de infraestrutura de TI, instalação e hospedagem de servidores</t>
+          <t>Serviço de Processamento de Dados</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2017NE00598</t>
+          <t>2017NE00628</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>20632.13</v>
+        <v>35178.08</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6641,19 +6641,19 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Serviço de Processamento de Dados</t>
+          <t>Ref. serviço de infraestrutura de TI, instalação e hospedagem de servidores</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025NE0000004</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>431973.43</v>
+        <v>10779.72</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6671,19 +6671,19 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 07.</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000004</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>10779.72</v>
+        <v>431973.43</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6701,28 +6701,24 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 07.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2024NE0000014</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>7/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000033</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>501859.7</v>
+        <v>669470.2</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6731,7 +6727,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do cetam. Parecer juridico - 2023 -PJ/CETAM pag. 28 a 33. TC: 0007/20</t>
+          <t>Referente a anulação da NE 015/2024 para ajuste da referência do artigo</t>
         </is>
       </c>
     </row>
@@ -6768,17 +6764,21 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2024NE0000033</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
+          <t>2024NE0000014</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>7/2020</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>669470.2</v>
+        <v>501859.7</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6787,19 +6787,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Referente a anulação da NE 015/2024 para ajuste da referência do artigo</t>
+          <t>contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do cetam. Parecer juridico - 2023 -PJ/CETAM pag. 28 a 33. TC: 0007/20</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2020NE00010</t>
+          <t>2020NE00027</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>339080.64</v>
+        <v>75482.55</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6817,19 +6817,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de circuito de transmissão de dados e acesso gerenciado a Rede Mundial _ internet.</t>
+          <t>Contratação de empresa especializada em tecnologia da informação para o desenvolvimento do modulo de inscrição e matricula, licenciamento de uso de sistemas integrados com os respectivos serviços de i</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2020NE00008</t>
+          <t>2020NE00009</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>63262.92</v>
+        <v>18910.8</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6847,19 +6847,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2020NE00009</t>
+          <t>2020NE00008</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>18910.8</v>
+        <v>63262.92</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6877,19 +6877,19 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação dos serviços de execução dos sistemas SPROWEB, Prodam Rh e Licenca do uso do gestor de conteudo web.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2020NE00027</t>
+          <t>2020NE00010</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>75482.55</v>
+        <v>339080.64</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6907,19 +6907,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em tecnologia da informação para o desenvolvimento do modulo de inscrição e matricula, licenciamento de uso de sistemas integrados com os respectivos serviços de i</t>
+          <t>Contratação dos serviços de circuito de transmissão de dados e acesso gerenciado a Rede Mundial _ internet.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
+          <t>2019NE00002</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>17098.47</v>
+        <v>17589.04</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6937,19 +6937,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços da TIC, compreendendo a execução dos sistemas SPROWEB, PRODAM E RH, e licença do uso do gestor de conteudo web</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2019NE00002</t>
+          <t>2019NE00003</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>17589.04</v>
+        <v>17098.47</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6967,19 +6967,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação de empresa especializada na prestação de serviços da TIC, compreendendo a execução dos sistemas SPROWEB, PRODAM E RH, e licença do uso do gestor de conteudo web</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2018NE00017</t>
+          <t>2018NE00027</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>17589.04</v>
+        <v>46422.27</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>Contratação dos serviços de tecnologia de informação para execução dos sistemas SPROWEb e PRODAMRH, e do site institucional parametrizável para atender demanda do CETAM.</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2018NE00027</t>
+          <t>2018NE00017</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7048,7 +7048,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>46422.27</v>
+        <v>17589.04</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7057,19 +7057,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia de informação para execução dos sistemas SPROWEb e PRODAMRH, e do site institucional parametrizável para atender demanda do CETAM.</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2017NE00005</t>
+          <t>2017NE00004</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>142280</v>
+        <v>20632.13</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7087,21 +7087,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Ref. seviço de processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2017NE00018</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2017NE00017</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
           <t>02/01/2017</t>
@@ -7117,17 +7113,21 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Anulação da NE nº 4, para acerto na modalidade</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2017NE00017</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr"/>
+          <t>2017NE00018</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C226" t="inlineStr">
         <is>
           <t>02/01/2017</t>
@@ -7143,19 +7143,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 4, para acerto na modalidade</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2017NE00004</t>
+          <t>2017NE00005</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>20632.13</v>
+        <v>142280</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7173,19 +7173,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ref. seviço de processamento de dados</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2014NE00048</t>
+          <t>2014NE00038</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1/2011</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>19140.72</v>
+        <v>6812</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7203,19 +7203,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Contrato No. 1/2011 - Acesso Computador Central / Link ponto a ponto 3 Mbps</t>
+          <t>Contrato No. 1/2012 - CFPP - Cadastro e Folha de Pagamento de Pessoal</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2014NE00038</t>
+          <t>2014NE00048</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>1/2011</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>6812</v>
+        <v>19140.72</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7233,21 +7233,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Contrato No. 1/2012 - CFPP - Cadastro e Folha de Pagamento de Pessoal</t>
+          <t>Contrato No. 1/2011 - Acesso Computador Central / Link ponto a ponto 3 Mbps</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021NE0001823</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>7/2020</t>
-        </is>
-      </c>
+          <t>2021NE0001818</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
         <is>
           <t>01/12/2021</t>
@@ -7263,17 +7259,21 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negócio, sob demanda.</t>
+          <t>Para correção do processo</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021NE0001818</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
+          <t>2021NE0001823</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>7/2020</t>
+        </is>
+      </c>
       <c r="C231" t="inlineStr">
         <is>
           <t>01/12/2021</t>
@@ -7289,19 +7289,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Para correção do processo</t>
+          <t>Contratação dos serviços de administração e suporte técnico em banco de dados e sistemas, desenvolvimento de sistemas de informação e modelagem de processos de negócio, sob demanda.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2016NE02171</t>
+          <t>2016NE02140</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>35570</v>
+        <v>5158.03</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7319,24 +7319,28 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Teleprocessamento</t>
+          <t>Re. cont. de serviço de informática</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2016NE02172</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
+          <t>2016NE02154</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C233" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>5158.03</v>
+        <v>35570</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7345,24 +7349,28 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Anulação para correção de data</t>
+          <t>Ref. a serviços de informática</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2016NE02170</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr"/>
+          <t>2016NE02173</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C234" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>35570</v>
+        <v>5158.03</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7371,28 +7379,24 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Anulação da NE para correção da moldalidade</t>
+          <t>Processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2016NE02173</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE02170</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>5158.03</v>
+        <v>35570</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7401,28 +7405,24 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Processamento de dados</t>
+          <t>Anulação da NE para correção da moldalidade</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2016NE02154</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2016NE02172</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>35570</v>
+        <v>5158.03</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7431,19 +7431,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ref. a serviços de informática</t>
+          <t>Anulação para correção de data</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2016NE02140</t>
+          <t>2016NE02171</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>5158.03</v>
+        <v>35570</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7461,19 +7461,19 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Re. cont. de serviço de informática</t>
+          <t>Teleprocessamento</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2017NE01736</t>
+          <t>2017NE01719</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>35565.1</v>
+        <v>5158.03</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7491,17 +7491,21 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
+          <t>Contratação dos serviços de tecnologia de informação para execução dos sistemas SPROWEb e PRODAMRH, e do site institucional parametrizável para atender demanda do CETAM.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2017NE01735</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
+          <t>2017NE01732</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C239" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -7517,7 +7521,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Anulação total</t>
+          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
         </is>
       </c>
     </row>
@@ -7554,14 +7558,10 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2017NE01732</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2017NE01735</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -7577,19 +7577,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
+          <t>Anulação total</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2017NE01719</t>
+          <t>2017NE01736</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>5158.03</v>
+        <v>35565.1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7607,14 +7607,14 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia de informação para execução dos sistemas SPROWEb e PRODAMRH, e do site institucional parametrizável para atender demanda do CETAM.</t>
+          <t>Contratação de empresa especializada em serviços de fornecimento de acesso a rede mundial de computadores - internet capital.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2016NE01897</t>
+          <t>2016NE01909</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>5158.03</v>
+        <v>35570</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7633,24 +7633,28 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Ref. despesa com processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2016NE01918</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>2016NE01897</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>01/11/2016</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>35570</v>
+        <v>5158.03</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7666,7 +7670,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2016NE01918</t>
+          <t>2016NE01909</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7689,14 +7693,14 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ref. serviço de processamento de dados</t>
+          <t>Ref. despesa com processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2016NE01909</t>
+          <t>2016NE01918</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7719,28 +7723,24 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ref. despesa com processamento de dados</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2016NE01897</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01918</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
           <t>01/11/2016</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>5158.03</v>
+        <v>35570</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2016NE01909</t>
+          <t>2016NE01897</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>35570</v>
+        <v>5158.03</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ref. despesa com processamento de dados</t>
+          <t>Ref. serviço de processamento de dados</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025NE0001022</t>
+          <t>2025NE0001021</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>469030.6</v>
+        <v>5389.86</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7831,19 +7831,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 09.</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025NE0001020</t>
+          <t>2025NE0001019</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>349894.99</v>
+        <v>185549.44</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7861,19 +7861,19 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025NE0001019</t>
+          <t>2025NE0001020</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>185549.44</v>
+        <v>349894.99</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7891,19 +7891,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação, compreendendo aos serviços de hospedagem de servidores e licença de uso de office 365, para atender as demandas do cetam.</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025NE0001021</t>
+          <t>2025NE0001022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>5389.86</v>
+        <v>469030.6</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>Contratação dos serviços de desenvolvimento de sistema de informação e modelagem de processos de negócios para atender as demandas do CETAM. TC: 0007/2020 AD: 09.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2019NE01409</t>
+          <t>2019NE01406</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>3418.74</v>
+        <v>5630.79</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2019NE01407</t>
+          <t>2019NE01405</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>872.62</v>
+        <v>6789.93</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2019NE01405</t>
+          <t>2019NE01407</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>6789.93</v>
+        <v>872.62</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2019NE01406</t>
+          <t>2019NE01409</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>5630.79</v>
+        <v>3418.74</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8058,12 +8058,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2024NE0000830</t>
+          <t>2024NE0000831</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>15/2021</t>
+          <t>6/2020</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>10339.26</v>
+        <v>669470.2</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
         </is>
       </c>
     </row>
@@ -8118,12 +8118,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2024NE0000831</t>
+          <t>2024NE0000830</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>6/2020</t>
+          <t>15/2021</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>669470.2</v>
+        <v>10339.26</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8141,19 +8141,19 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE INTERLIGAÇÃO DAS REDES DE COMPUTADORES DAS UNIDADES DO CETAM MEDIANTE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS E CONEXAO A REDE METROPOLITANA DE MANAUS(METROMAO). P</t>
+          <t>Contratação da prestação de serviços de TIC, compreendendo a Execução dos sistemas SPROweb, Licença de uso do Gestor de Conteúdo Web e PRODAM RH, para atender as demandas do CETAM. TC: 0015/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2016NE01211</t>
+          <t>2016NE01213</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4203.74</v>
+        <v>5612.46</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8208,12 +8208,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2016NE01213</t>
+          <t>2016NE01211</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>5612.46</v>
+        <v>4203.74</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2015NE01192</t>
+          <t>2015NE01185</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Anulação total</t>
+          <t>Celebração do contrato Sproweb</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2015NE01185</t>
+          <t>2015NE01192</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8291,19 +8291,19 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Celebração do contrato Sproweb</t>
+          <t>Anulação total</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2015NE00035</t>
+          <t>2015NE00036</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8312,7 +8312,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>17901</v>
+        <v>1799.56</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8328,12 +8328,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2015NE00036</t>
+          <t>2015NE00035</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1799.56</v>
+        <v>17901</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8388,14 +8388,10 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2018NE00093</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2018NE00096</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
           <t>01/03/2018</t>
@@ -8411,28 +8407,24 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>contratação dos serviços de fornecimento de acesso a rede mundial de computadores - internet capital</t>
+          <t>Anulação total</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2018NE00095</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2018NE00068</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
         <is>
           <t>01/03/2018</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>42385.53</v>
+        <v>17589.04</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8441,19 +8433,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de tecnologia da informação para execução dos sistemas de SPROWEB e PRODAMRH</t>
+          <t>Anulação da NE</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2018NE00097</t>
+          <t>2018NE00094</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2017</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8462,7 +8454,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>248955.7</v>
+        <v>17589.04</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8471,14 +8463,14 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>contratação dos serviços de fornecimento de acesso a rede mundial de computadores - internet capital</t>
+          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2018NE00070</t>
+          <t>2018NE00069</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -8488,7 +8480,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>248955.7</v>
+        <v>42385.53</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8504,7 +8496,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2018NE00069</t>
+          <t>2018NE00070</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -8514,7 +8506,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>42385.53</v>
+        <v>248955.7</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8530,12 +8522,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2018NE00094</t>
+          <t>2018NE00097</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>4/2017</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8544,7 +8536,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>17589.04</v>
+        <v>248955.7</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8553,24 +8545,28 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prover serviços de infraestrutura de tecnologia da informação, compreendendo os serviços de instalação e hospedagem de servidores e suporte em sistema de inform</t>
+          <t>contratação dos serviços de fornecimento de acesso a rede mundial de computadores - internet capital</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2018NE00068</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
+          <t>2018NE00095</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
           <t>01/03/2018</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>17589.04</v>
+        <v>42385.53</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8579,17 +8575,21 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Anulação da NE</t>
+          <t>Contratação dos serviços de tecnologia da informação para execução dos sistemas de SPROWEB e PRODAMRH</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2018NE00096</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr"/>
+          <t>2018NE00093</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C277" t="inlineStr">
         <is>
           <t>01/03/2018</t>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Anulação total</t>
+          <t>contratação dos serviços de fornecimento de acesso a rede mundial de computadores - internet capital</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/CETAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CETAM/dossie.xlsx
@@ -577,7 +577,11 @@
           <t>data_prescricao_proxima</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2031-03-31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
